--- a/artfynd/A 7824-2025 artfynd.xlsx
+++ b/artfynd/A 7824-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123414202</v>
+        <v>123414050</v>
       </c>
       <c r="B2" t="n">
-        <v>56691</v>
+        <v>57497</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575790</v>
+        <v>575711</v>
       </c>
       <c r="R2" t="n">
-        <v>6378989</v>
+        <v>6378919</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,11 +759,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -904,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123414219</v>
+        <v>123414092</v>
       </c>
       <c r="B4" t="n">
-        <v>57851</v>
+        <v>57497</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,20 +907,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -937,16 +928,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -956,13 +943,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575790</v>
+        <v>575702</v>
       </c>
       <c r="R4" t="n">
-        <v>6378989</v>
+        <v>6378922</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1018,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123414124</v>
+        <v>123414219</v>
       </c>
       <c r="B5" t="n">
-        <v>57634</v>
+        <v>57851</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,25 +1017,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1060,7 +1047,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1070,10 +1057,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575692</v>
+        <v>575790</v>
       </c>
       <c r="R5" t="n">
-        <v>6378990</v>
+        <v>6378989</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1132,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123414092</v>
+        <v>123414202</v>
       </c>
       <c r="B6" t="n">
-        <v>57497</v>
+        <v>56691</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,35 +1131,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,13 +1171,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575702</v>
+        <v>575790</v>
       </c>
       <c r="R6" t="n">
-        <v>6378922</v>
+        <v>6378989</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,6 +1207,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123414050</v>
+        <v>123414124</v>
       </c>
       <c r="B7" t="n">
-        <v>57497</v>
+        <v>57634</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,29 +1254,33 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575711</v>
+        <v>575692</v>
       </c>
       <c r="R7" t="n">
-        <v>6378919</v>
+        <v>6378990</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 7824-2025 artfynd.xlsx
+++ b/artfynd/A 7824-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123414050</v>
+        <v>123414092</v>
       </c>
       <c r="B2" t="n">
         <v>57497</v>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575711</v>
+        <v>575702</v>
       </c>
       <c r="R2" t="n">
-        <v>6378919</v>
+        <v>6378922</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123414161</v>
+        <v>123414202</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>56691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,35 +797,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575787</v>
+        <v>575790</v>
       </c>
       <c r="R3" t="n">
-        <v>6378988</v>
+        <v>6378989</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,6 +873,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123414092</v>
+        <v>123414050</v>
       </c>
       <c r="B4" t="n">
         <v>57497</v>
@@ -943,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575702</v>
+        <v>575711</v>
       </c>
       <c r="R4" t="n">
-        <v>6378922</v>
+        <v>6378919</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123414219</v>
+        <v>123414124</v>
       </c>
       <c r="B5" t="n">
-        <v>57851</v>
+        <v>57634</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,25 +1026,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1047,7 +1056,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1057,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575790</v>
+        <v>575692</v>
       </c>
       <c r="R5" t="n">
-        <v>6378989</v>
+        <v>6378990</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1119,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123414202</v>
+        <v>123414161</v>
       </c>
       <c r="B6" t="n">
-        <v>56691</v>
+        <v>57497</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,39 +1140,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1171,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575790</v>
+        <v>575787</v>
       </c>
       <c r="R6" t="n">
-        <v>6378989</v>
+        <v>6378988</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,11 +1212,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123414124</v>
+        <v>123414219</v>
       </c>
       <c r="B7" t="n">
-        <v>57634</v>
+        <v>57851</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,25 +1250,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1280,7 +1280,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575692</v>
+        <v>575790</v>
       </c>
       <c r="R7" t="n">
-        <v>6378990</v>
+        <v>6378989</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 7824-2025 artfynd.xlsx
+++ b/artfynd/A 7824-2025 artfynd.xlsx
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123414161</v>
+        <v>123414219</v>
       </c>
       <c r="B6" t="n">
-        <v>57497</v>
+        <v>57851</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,20 +1140,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1161,12 +1161,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1176,13 +1180,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575787</v>
+        <v>575790</v>
       </c>
       <c r="R6" t="n">
-        <v>6378988</v>
+        <v>6378989</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1238,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123414219</v>
+        <v>123414161</v>
       </c>
       <c r="B7" t="n">
-        <v>57851</v>
+        <v>57497</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,20 +1254,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1271,16 +1275,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575790</v>
+        <v>575787</v>
       </c>
       <c r="R7" t="n">
-        <v>6378989</v>
+        <v>6378988</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 7824-2025 artfynd.xlsx
+++ b/artfynd/A 7824-2025 artfynd.xlsx
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123414202</v>
+        <v>123414050</v>
       </c>
       <c r="B3" t="n">
-        <v>56691</v>
+        <v>57497</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,39 +797,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575790</v>
+        <v>575711</v>
       </c>
       <c r="R3" t="n">
-        <v>6378989</v>
+        <v>6378919</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,11 +869,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123414050</v>
+        <v>123414202</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>56691</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,35 +907,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -952,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575711</v>
+        <v>575790</v>
       </c>
       <c r="R4" t="n">
-        <v>6378919</v>
+        <v>6378989</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -988,6 +983,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123414124</v>
+        <v>123414161</v>
       </c>
       <c r="B5" t="n">
-        <v>57634</v>
+        <v>57497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,33 +1030,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1066,13 +1062,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575692</v>
+        <v>575787</v>
       </c>
       <c r="R5" t="n">
-        <v>6378990</v>
+        <v>6378988</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1128,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123414219</v>
+        <v>123414124</v>
       </c>
       <c r="B6" t="n">
-        <v>57851</v>
+        <v>57634</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1136,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1170,7 +1166,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1180,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575790</v>
+        <v>575692</v>
       </c>
       <c r="R6" t="n">
-        <v>6378989</v>
+        <v>6378990</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1242,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123414161</v>
+        <v>123414219</v>
       </c>
       <c r="B7" t="n">
-        <v>57497</v>
+        <v>57851</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,20 +1250,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1275,12 +1271,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575787</v>
+        <v>575790</v>
       </c>
       <c r="R7" t="n">
-        <v>6378988</v>
+        <v>6378989</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 7824-2025 artfynd.xlsx
+++ b/artfynd/A 7824-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123414219</v>
+        <v>123414202</v>
       </c>
       <c r="B2" t="n">
-        <v>57851</v>
+        <v>56697</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,12 +714,12 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -763,6 +763,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +797,7 @@
         <v>123414161</v>
       </c>
       <c r="B3" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123414092</v>
+        <v>123414050</v>
       </c>
       <c r="B4" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,10 +952,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575702</v>
+        <v>575711</v>
       </c>
       <c r="R4" t="n">
-        <v>6378922</v>
+        <v>6378919</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123414124</v>
+        <v>123414092</v>
       </c>
       <c r="B5" t="n">
-        <v>57634</v>
+        <v>57503</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,33 +1030,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1061,13 +1062,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575692</v>
+        <v>575702</v>
       </c>
       <c r="R5" t="n">
-        <v>6378990</v>
+        <v>6378922</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123414202</v>
+        <v>123414124</v>
       </c>
       <c r="B6" t="n">
-        <v>56691</v>
+        <v>57640</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,25 +1136,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1162,12 +1163,12 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1175,10 +1176,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575790</v>
+        <v>575692</v>
       </c>
       <c r="R6" t="n">
-        <v>6378989</v>
+        <v>6378990</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1211,11 +1212,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123414050</v>
+        <v>123414219</v>
       </c>
       <c r="B7" t="n">
-        <v>57497</v>
+        <v>57857</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,20 +1250,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1275,12 +1271,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575711</v>
+        <v>575790</v>
       </c>
       <c r="R7" t="n">
-        <v>6378919</v>
+        <v>6378989</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 7824-2025 artfynd.xlsx
+++ b/artfynd/A 7824-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123414202</v>
+        <v>123414124</v>
       </c>
       <c r="B2" t="n">
-        <v>56697</v>
+        <v>57643</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,12 +714,12 @@
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575790</v>
+        <v>575692</v>
       </c>
       <c r="R2" t="n">
-        <v>6378989</v>
+        <v>6378990</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -763,11 +763,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123414161</v>
+        <v>123414219</v>
       </c>
       <c r="B3" t="n">
-        <v>57503</v>
+        <v>57860</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,20 +801,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -827,12 +822,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -842,13 +841,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575787</v>
+        <v>575790</v>
       </c>
       <c r="R3" t="n">
-        <v>6378988</v>
+        <v>6378989</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -904,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123414050</v>
+        <v>123414092</v>
       </c>
       <c r="B4" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,10 +951,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575711</v>
+        <v>575702</v>
       </c>
       <c r="R4" t="n">
-        <v>6378919</v>
+        <v>6378922</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,10 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123414092</v>
+        <v>123414161</v>
       </c>
       <c r="B5" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,7 +1051,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1062,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575702</v>
+        <v>575787</v>
       </c>
       <c r="R5" t="n">
-        <v>6378922</v>
+        <v>6378988</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123414124</v>
+        <v>123414050</v>
       </c>
       <c r="B6" t="n">
-        <v>57640</v>
+        <v>57506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,33 +1139,29 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1176,13 +1171,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575692</v>
+        <v>575711</v>
       </c>
       <c r="R6" t="n">
-        <v>6378990</v>
+        <v>6378919</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1238,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123414219</v>
+        <v>123414202</v>
       </c>
       <c r="B7" t="n">
-        <v>57857</v>
+        <v>56700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,21 +1249,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1277,12 +1272,12 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1326,6 +1321,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 7824-2025 artfynd.xlsx
+++ b/artfynd/A 7824-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123414124</v>
+        <v>123414161</v>
       </c>
       <c r="B2" t="n">
-        <v>57643</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,33 +691,29 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575692</v>
+        <v>575787</v>
       </c>
       <c r="R2" t="n">
-        <v>6378990</v>
+        <v>6378988</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -789,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123414219</v>
+        <v>123414202</v>
       </c>
       <c r="B3" t="n">
-        <v>57860</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -805,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -828,12 +824,12 @@
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -877,6 +873,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123414092</v>
+        <v>123414219</v>
       </c>
       <c r="B4" t="n">
-        <v>57506</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,20 +916,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -936,12 +937,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -951,13 +956,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575702</v>
+        <v>575790</v>
       </c>
       <c r="R4" t="n">
-        <v>6378922</v>
+        <v>6378989</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1013,10 +1018,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123414161</v>
+        <v>123414124</v>
       </c>
       <c r="B5" t="n">
-        <v>57506</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,29 +1034,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1061,13 +1070,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575787</v>
+        <v>575692</v>
       </c>
       <c r="R5" t="n">
-        <v>6378988</v>
+        <v>6378990</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1132,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123414050</v>
+        <v>123414092</v>
       </c>
       <c r="B6" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1171,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575711</v>
+        <v>575702</v>
       </c>
       <c r="R6" t="n">
-        <v>6378919</v>
+        <v>6378922</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1233,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123414202</v>
+        <v>123414050</v>
       </c>
       <c r="B7" t="n">
-        <v>56700</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,39 +1254,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1285,13 +1290,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575790</v>
+        <v>575711</v>
       </c>
       <c r="R7" t="n">
-        <v>6378989</v>
+        <v>6378919</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1321,11 +1326,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 7824-2025 artfynd.xlsx
+++ b/artfynd/A 7824-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123414161</v>
+        <v>123414050</v>
       </c>
       <c r="B2" t="n">
         <v>57507</v>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575787</v>
+        <v>575711</v>
       </c>
       <c r="R2" t="n">
-        <v>6378988</v>
+        <v>6378919</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123414202</v>
+        <v>123414092</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,39 +797,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575790</v>
+        <v>575702</v>
       </c>
       <c r="R3" t="n">
-        <v>6378989</v>
+        <v>6378922</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,11 +869,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123414219</v>
+        <v>123414124</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>57644</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +907,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -946,7 +937,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -956,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575790</v>
+        <v>575692</v>
       </c>
       <c r="R4" t="n">
-        <v>6378989</v>
+        <v>6378990</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1018,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123414124</v>
+        <v>123414161</v>
       </c>
       <c r="B5" t="n">
-        <v>57644</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,33 +1025,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1070,13 +1057,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575692</v>
+        <v>575787</v>
       </c>
       <c r="R5" t="n">
-        <v>6378990</v>
+        <v>6378988</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,10 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123414092</v>
+        <v>123414202</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>56700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,35 +1131,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1180,13 +1171,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575702</v>
+        <v>575790</v>
       </c>
       <c r="R6" t="n">
-        <v>6378922</v>
+        <v>6378989</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,6 +1207,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123414050</v>
+        <v>123414219</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,20 +1250,20 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1275,12 +1271,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575711</v>
+        <v>575790</v>
       </c>
       <c r="R7" t="n">
-        <v>6378919</v>
+        <v>6378989</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>

--- a/artfynd/A 7824-2025 artfynd.xlsx
+++ b/artfynd/A 7824-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123414050</v>
+        <v>123414219</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,12 +708,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575711</v>
+        <v>575790</v>
       </c>
       <c r="R2" t="n">
-        <v>6378919</v>
+        <v>6378989</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -785,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123414092</v>
+        <v>123414050</v>
       </c>
       <c r="B3" t="n">
         <v>57507</v>
@@ -833,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575702</v>
+        <v>575711</v>
       </c>
       <c r="R3" t="n">
-        <v>6378922</v>
+        <v>6378919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123414124</v>
+        <v>123414092</v>
       </c>
       <c r="B4" t="n">
-        <v>57644</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,33 +915,29 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575692</v>
+        <v>575702</v>
       </c>
       <c r="R4" t="n">
-        <v>6378990</v>
+        <v>6378922</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1238,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123414219</v>
+        <v>123414124</v>
       </c>
       <c r="B7" t="n">
-        <v>57861</v>
+        <v>57644</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,25 +1250,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1280,7 +1280,7 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575790</v>
+        <v>575692</v>
       </c>
       <c r="R7" t="n">
-        <v>6378989</v>
+        <v>6378990</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 7824-2025 artfynd.xlsx
+++ b/artfynd/A 7824-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123414219</v>
+        <v>123414050</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,16 +708,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +723,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575790</v>
+        <v>575711</v>
       </c>
       <c r="R2" t="n">
-        <v>6378989</v>
+        <v>6378919</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -789,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123414050</v>
+        <v>123414092</v>
       </c>
       <c r="B3" t="n">
         <v>57507</v>
@@ -837,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575711</v>
+        <v>575702</v>
       </c>
       <c r="R3" t="n">
-        <v>6378919</v>
+        <v>6378922</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123414092</v>
+        <v>123414219</v>
       </c>
       <c r="B4" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,20 +907,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -932,12 +928,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -947,13 +947,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575702</v>
+        <v>575790</v>
       </c>
       <c r="R4" t="n">
-        <v>6378922</v>
+        <v>6378989</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1009,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123414161</v>
+        <v>123414124</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>57644</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,29 +1025,33 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1057,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575787</v>
+        <v>575692</v>
       </c>
       <c r="R5" t="n">
-        <v>6378988</v>
+        <v>6378990</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1119,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123414202</v>
+        <v>123414161</v>
       </c>
       <c r="B6" t="n">
-        <v>56700</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1131,39 +1135,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1171,13 +1171,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575790</v>
+        <v>575787</v>
       </c>
       <c r="R6" t="n">
-        <v>6378989</v>
+        <v>6378988</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1207,11 +1207,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123414124</v>
+        <v>123414202</v>
       </c>
       <c r="B7" t="n">
-        <v>57644</v>
+        <v>56700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,25 +1245,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1277,12 +1272,12 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1290,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575692</v>
+        <v>575790</v>
       </c>
       <c r="R7" t="n">
-        <v>6378990</v>
+        <v>6378989</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1326,6 +1321,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 7824-2025 artfynd.xlsx
+++ b/artfynd/A 7824-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123414050</v>
+        <v>123414161</v>
       </c>
       <c r="B2" t="n">
         <v>57507</v>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575711</v>
+        <v>575787</v>
       </c>
       <c r="R2" t="n">
-        <v>6378919</v>
+        <v>6378988</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,7 +785,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123414092</v>
+        <v>123414050</v>
       </c>
       <c r="B3" t="n">
         <v>57507</v>
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575702</v>
+        <v>575711</v>
       </c>
       <c r="R3" t="n">
-        <v>6378922</v>
+        <v>6378919</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -895,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123414219</v>
+        <v>123414202</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -934,12 +934,12 @@
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -983,6 +983,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123414124</v>
+        <v>123414092</v>
       </c>
       <c r="B5" t="n">
-        <v>57644</v>
+        <v>57507</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1025,33 +1030,29 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1061,13 +1062,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575692</v>
+        <v>575702</v>
       </c>
       <c r="R5" t="n">
-        <v>6378990</v>
+        <v>6378922</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1123,10 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123414161</v>
+        <v>123414219</v>
       </c>
       <c r="B6" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1135,20 +1136,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1156,12 +1157,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1171,13 +1176,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>575787</v>
+        <v>575790</v>
       </c>
       <c r="R6" t="n">
-        <v>6378988</v>
+        <v>6378989</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1233,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123414202</v>
+        <v>123414124</v>
       </c>
       <c r="B7" t="n">
-        <v>56700</v>
+        <v>57644</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,25 +1250,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1272,12 +1277,12 @@
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1285,10 +1290,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575790</v>
+        <v>575692</v>
       </c>
       <c r="R7" t="n">
-        <v>6378989</v>
+        <v>6378990</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1321,11 +1326,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 7824-2025 artfynd.xlsx
+++ b/artfynd/A 7824-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123414161</v>
+        <v>123414050</v>
       </c>
       <c r="B2" t="n">
         <v>57507</v>
@@ -713,7 +713,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575787</v>
+        <v>575711</v>
       </c>
       <c r="R2" t="n">
-        <v>6378988</v>
+        <v>6378919</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -785,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123414050</v>
+        <v>123414202</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,35 +797,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575711</v>
+        <v>575790</v>
       </c>
       <c r="R3" t="n">
-        <v>6378919</v>
+        <v>6378989</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,6 +873,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123414202</v>
+        <v>123414161</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,39 +916,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -947,13 +952,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575790</v>
+        <v>575787</v>
       </c>
       <c r="R4" t="n">
-        <v>6378989</v>
+        <v>6378988</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -983,11 +988,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 7824-2025 artfynd.xlsx
+++ b/artfynd/A 7824-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123414050</v>
+        <v>123414124</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,29 +691,33 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -723,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>575711</v>
+        <v>575692</v>
       </c>
       <c r="R2" t="n">
-        <v>6378919</v>
+        <v>6378990</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -785,10 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123414202</v>
+        <v>123414050</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,39 +801,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,13 +837,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>575790</v>
+        <v>575711</v>
       </c>
       <c r="R3" t="n">
-        <v>6378989</v>
+        <v>6378919</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -873,11 +873,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123414161</v>
+        <v>123414092</v>
       </c>
       <c r="B4" t="n">
         <v>57507</v>
@@ -942,7 +937,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -952,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>575787</v>
+        <v>575702</v>
       </c>
       <c r="R4" t="n">
-        <v>6378988</v>
+        <v>6378922</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123414092</v>
+        <v>123414219</v>
       </c>
       <c r="B5" t="n">
-        <v>57507</v>
+        <v>57861</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,20 +1021,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1047,12 +1042,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1062,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>575702</v>
+        <v>575790</v>
       </c>
       <c r="R5" t="n">
-        <v>6378922</v>
+        <v>6378989</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1124,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123414219</v>
+        <v>123414202</v>
       </c>
       <c r="B6" t="n">
-        <v>57861</v>
+        <v>56700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,12 +1162,12 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1212,6 +1211,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Flög upp från marken</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123414124</v>
+        <v>123414161</v>
       </c>
       <c r="B7" t="n">
-        <v>57644</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,33 +1258,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
@@ -1290,13 +1290,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>575692</v>
+        <v>575787</v>
       </c>
       <c r="R7" t="n">
-        <v>6378990</v>
+        <v>6378988</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
